--- a/data/metadata.xlsx
+++ b/data/metadata.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\blawid\YMV-Nextstrain\Nextstrain-YMV-Brazil-main\Nextstrain-YMV-Brazil-main\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E587B2F-69D3-4A15-83FC-91204816FEBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32781545-D672-4864-9AE6-39D05B3080E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{8603F63E-B687-487D-9488-22555794FF28}"/>
   </bookViews>
@@ -4316,9 +4316,12 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Ênfase1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -21013,7 +21016,7 @@
       <c r="C565" t="s">
         <v>11</v>
       </c>
-      <c r="D565">
+      <c r="D565" s="2">
         <v>608</v>
       </c>
       <c r="E565" t="s">
